--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104655_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104655_W22.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.240500000000001</v>
+        <v>7.6244</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2547</v>
+        <v>4.464</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9858</v>
+        <v>3.1604</v>
       </c>
       <c r="G2" t="n">
-        <v>5.0223</v>
+        <v>5.02</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1545</v>
+        <v>1.1437</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8678</v>
+        <v>3.8764</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1225</v>
+        <v>4.0834</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0625</v>
+        <v>1.03</v>
       </c>
       <c r="L2" t="n">
-        <v>3.06</v>
+        <v>3.0534</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8998</v>
+        <v>0.9366</v>
       </c>
       <c r="N2" t="n">
-        <v>0.092</v>
+        <v>0.1137</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8078</v>
+        <v>0.8229</v>
       </c>
       <c r="P2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7607</v>
+        <v>1.1523</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1433</v>
+        <v>0.4129</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6174</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0965</v>
+        <v>0.0863</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3499</v>
+        <v>1.3336</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7262</v>
+        <v>6.6728</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1522</v>
+        <v>4.8409</v>
       </c>
       <c r="F3" t="n">
-        <v>1.574</v>
+        <v>1.832</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4228</v>
+        <v>4.4173</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1385</v>
+        <v>2.1369</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2843</v>
+        <v>2.2804</v>
       </c>
       <c r="J3" t="n">
-        <v>4.613</v>
+        <v>4.573</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3523</v>
+        <v>3.33</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2607</v>
+        <v>1.243</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1902</v>
+        <v>-0.1557</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2139</v>
+        <v>-1.1931</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0237</v>
+        <v>1.0374</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2845</v>
+        <v>-0.3379</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0071</v>
+        <v>-0.2769</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2774</v>
+        <v>-0.0611</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.578</v>
+        <v>3.8993</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6826</v>
+        <v>0.9962</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8954</v>
+        <v>2.9031</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6386</v>
+        <v>3.6122</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9087</v>
+        <v>-0.9294</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5473</v>
+        <v>4.5416</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0276</v>
+        <v>1.9744</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.0643</v>
+        <v>-1.1009</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0919</v>
+        <v>3.0753</v>
       </c>
       <c r="M4" t="n">
-        <v>1.6111</v>
+        <v>1.6377</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1556</v>
+        <v>0.1715</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4555</v>
+        <v>1.4663</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5538</v>
+        <v>0.9002</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0575</v>
+        <v>0.4363</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4963</v>
+        <v>0.4639</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>M. NGOUAMA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7411</v>
+        <v>0.9852</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.2686</v>
+        <v>-0.9389999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0097</v>
+        <v>1.9241</v>
       </c>
       <c r="G5" t="n">
-        <v>0.922</v>
+        <v>-1.0058</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8499</v>
+        <v>-0.3624</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07199999999999999</v>
+        <v>-0.6433</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3082</v>
+        <v>-0.8385</v>
       </c>
       <c r="K5" t="n">
-        <v>0.159</v>
+        <v>0.041</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1493</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6138</v>
+        <v>-0.1673</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6909999999999999</v>
+        <v>-0.4034</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0772</v>
+        <v>0.2361</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.4952</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1809</v>
+        <v>-0.079</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.018</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0992</v>
+        <v>-0.097</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.9317</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. NGOUAMA</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2285</v>
+        <v>0.7052</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3484</v>
+        <v>-2.2691</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1199</v>
+        <v>2.9743</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0201</v>
+        <v>0.9282</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3724</v>
+        <v>0.8474</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0.0808</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8113</v>
+        <v>0.2933</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0551</v>
+        <v>0.1444</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8663999999999999</v>
+        <v>0.1489</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2088</v>
+        <v>0.6349</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4275</v>
+        <v>0.703</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2187</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2745</v>
+        <v>-0.223</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4294</v>
+        <v>-0.0585</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.845</v>
+        <v>-0.1645</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.349</v>
+        <v>0.2271</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9299</v>
+        <v>-1.4812</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5809</v>
+        <v>1.7082</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.294</v>
+        <v>-0.3035</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1602</v>
+        <v>-1.1549</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8662</v>
+        <v>0.8514</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1898</v>
+        <v>0.1524</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6549</v>
+        <v>-0.6657</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8448</v>
+        <v>0.8181</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4839</v>
+        <v>-0.4558</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5766</v>
+        <v>-0.993</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1462</v>
+        <v>-0.6532</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4304</v>
+        <v>-0.3399</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. DURAN</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5414</v>
+        <v>-0.2981</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.995</v>
+        <v>0.6052</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4537</v>
+        <v>-0.9033</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6291</v>
+        <v>0.0236</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1573</v>
+        <v>0.0056</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7864</v>
+        <v>0.018</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7864</v>
+        <v>0.6261</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.5516</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7864</v>
+        <v>0.0745</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1573</v>
+        <v>-0.6025</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1573</v>
+        <v>-0.546</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.0565</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.366</v>
+        <v>-0.1835</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2087</v>
+        <v>0.0278</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1573</v>
+        <v>-0.2113</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>E. DURAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6664</v>
+        <v>-0.425</v>
       </c>
       <c r="E9" t="n">
-        <v>0.309</v>
+        <v>-0.8803</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9754</v>
+        <v>0.4553</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0189</v>
+        <v>-0.6317</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0028</v>
+        <v>0.1579</v>
       </c>
       <c r="I9" t="n">
-        <v>0.016</v>
+        <v>-0.7896</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6288</v>
+        <v>-0.7896</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5541</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0746</v>
+        <v>-0.7896</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6099</v>
+        <v>0.1579</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5513</v>
+        <v>0.1579</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0586</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5511</v>
+        <v>-0.2486</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2782</v>
+        <v>-0.0907</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2728</v>
+        <v>-0.1579</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2011</v>
+        <v>-2.3985</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1546</v>
+        <v>-3.2942</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9535</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1566</v>
+        <v>-2.1627</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5192</v>
+        <v>-2.5324</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3626</v>
+        <v>0.3697</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0777</v>
+        <v>-2.1081</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.8884</v>
+        <v>-1.9143</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1893</v>
+        <v>-0.1939</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0789</v>
+        <v>-0.0546</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0897</v>
+        <v>0.9024</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9134</v>
+        <v>0.8218</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1763</v>
+        <v>0.0805</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2307</v>
+        <v>-2.623</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3299</v>
+        <v>-2.7428</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0992</v>
+        <v>0.1198</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1063</v>
+        <v>-2.0982</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.371</v>
+        <v>-0.3596</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.7353</v>
+        <v>-1.7385</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3742</v>
+        <v>-1.3814</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7321</v>
+        <v>-0.7168</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1905</v>
+        <v>-0.5947</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1785</v>
+        <v>-0.2232</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.369</v>
+        <v>-0.3714</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0308</v>
+        <v>-2.9503</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9953</v>
+        <v>-2.8681</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0355</v>
+        <v>-0.0822</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5687</v>
+        <v>-0.5625</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3216</v>
+        <v>0.3298</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8903</v>
+        <v>-0.8924</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3742</v>
+        <v>-1.3814</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8055</v>
+        <v>0.8189</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4621</v>
+        <v>-0.3878</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4869</v>
+        <v>-0.3485</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0248</v>
+        <v>-0.0392</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.0379</v>
+        <v>11.4191</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.623199999999999</v>
+        <v>-3.5684</v>
       </c>
       <c r="F13" t="n">
-        <v>14.6612</v>
+        <v>14.9874</v>
       </c>
       <c r="G13" t="n">
-        <v>7.249800000000001</v>
+        <v>7.2369</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7068999999999998</v>
+        <v>-0.7174000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>7.9565</v>
+        <v>7.954499999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>5.466100000000001</v>
+        <v>5.2036</v>
       </c>
       <c r="K13" t="n">
-        <v>1.748599999999999</v>
+        <v>1.588500000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>3.717600000000001</v>
+        <v>3.615</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7837</v>
+        <v>2.0333</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.4554</v>
+        <v>-2.3058</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2392</v>
+        <v>4.3392</v>
       </c>
       <c r="P13" t="n">
-        <v>3.4025</v>
+        <v>3.414499999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.8785</v>
+        <v>-15.9343</v>
       </c>
       <c r="R13" t="n">
-        <v>19.281</v>
+        <v>19.3486</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.482</v>
+        <v>-0.09259999999999974</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3454</v>
+        <v>0.06580000000000008</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1362999999999999</v>
+        <v>-0.1585</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8677000000000001</v>
+        <v>0.8601000000000003</v>
       </c>
       <c r="W13" t="n">
-        <v>7.1347</v>
+        <v>7.0965</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.266900000000001</v>
+        <v>-6.2361</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4968</v>
+        <v>3.3398</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1068</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3901</v>
+        <v>2.4734</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2</v>
+        <v>1.2112</v>
       </c>
       <c r="H14" t="n">
-        <v>0.339</v>
+        <v>0.3471</v>
       </c>
       <c r="I14" t="n">
-        <v>0.861</v>
+        <v>0.8641</v>
       </c>
       <c r="J14" t="n">
-        <v>0.698</v>
+        <v>0.695</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6234</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5019</v>
+        <v>0.5162</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5483</v>
+        <v>0.3774</v>
       </c>
       <c r="T14" t="n">
-        <v>0.248</v>
+        <v>0.0136</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3003</v>
+        <v>0.3637</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. PAULICAP</t>
+          <t>F. BASSAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2858</v>
+        <v>1.4558</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0131</v>
+        <v>-0.4091</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2989</v>
+        <v>1.8649</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9949</v>
+        <v>1.1421</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6479</v>
+        <v>1.4297</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.653</v>
+        <v>-0.2876</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0053</v>
+        <v>1.8269</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8934</v>
+        <v>1.7754</v>
       </c>
       <c r="L15" t="n">
-        <v>0.112</v>
+        <v>0.0515</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0104</v>
+        <v>-0.6847</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7546</v>
+        <v>-0.3457</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7649</v>
+        <v>-0.3391</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.8147</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.4952</v>
+        <v>-3.6421</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6805</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7841</v>
+        <v>0.2728</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1553</v>
+        <v>-0.2281</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6288</v>
+        <v>0.501</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3214</v>
+        <v>1.6342</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3214</v>
+        <v>1.6342</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.514</v>
+        <v>0.7621</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0522</v>
+        <v>0.066</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5662</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4305</v>
+        <v>0.4345</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3319</v>
+        <v>0.3331</v>
       </c>
       <c r="I16" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="O16" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1434</v>
+        <v>0.0999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0696</v>
+        <v>0.0487</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0738</v>
+        <v>0.0512</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. BASSAS</t>
+          <t>P. PAULICAP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0905</v>
+        <v>0.7229</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0777</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1682</v>
+        <v>1.3484</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1345</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4197</v>
+        <v>1.6431</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2852</v>
+        <v>-0.6446</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8501</v>
+        <v>0.994</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7836</v>
+        <v>0.8823</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0665</v>
+        <v>0.1117</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7157</v>
+        <v>0.0044</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3639</v>
+        <v>0.7608</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3517</v>
+        <v>-0.7563</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5878</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.6293</v>
+        <v>-2.5039</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0415</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0951</v>
+        <v>1.2299</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9376</v>
+        <v>0.5688</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1576</v>
+        <v>0.6611</v>
       </c>
       <c r="V17" t="n">
-        <v>1.639</v>
+        <v>0.3155</v>
       </c>
       <c r="W17" t="n">
-        <v>1.639</v>
+        <v>0.3155</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. KNUDSEN</t>
+          <t>R. OBASOHAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0613</v>
+        <v>0.0228</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9181</v>
+        <v>1.0299</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8569</v>
+        <v>-1.0071</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.0917</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8383</v>
+        <v>-0.129</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3359</v>
+        <v>0.2208</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6882</v>
+        <v>0.9805</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4373</v>
+        <v>0.9061</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.749</v>
+        <v>0.0745</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1858</v>
+        <v>-0.8888</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.599</v>
+        <v>-1.0351</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4132</v>
+        <v>0.1463</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1878</v>
+        <v>-0.3648</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2299</v>
+        <v>-0.3768</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4177</v>
+        <v>0.0119</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7071</v>
+        <v>-0.387</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7071</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ORIOLA</t>
+          <t>G. KNUDSEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2172</v>
+        <v>-0.0953</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8187</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6015</v>
+        <v>-0.6502</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3535</v>
+        <v>0.5062</v>
       </c>
       <c r="H19" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.8414</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4313</v>
+        <v>-0.3351</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2416</v>
+        <v>0.6783</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0142</v>
+        <v>1.4307</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2558</v>
+        <v>-0.7524</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5951</v>
+        <v>-0.172</v>
       </c>
       <c r="N19" t="n">
-        <v>0.092</v>
+        <v>-0.5893</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6871</v>
+        <v>0.4173</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.722</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2683</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6581</v>
+        <v>-0.3542</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4083</v>
+        <v>-0.1233</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2498</v>
+        <v>-0.2309</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9320000000000001</v>
+        <v>-0.7025</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3214</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. OBASOHAN</t>
+          <t>P. ORIOLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4841</v>
+        <v>-0.1546</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0664</v>
+        <v>-1.091</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5505</v>
+        <v>0.9364</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0878</v>
+        <v>-1.3396</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1255</v>
+        <v>0.0857</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2133</v>
+        <v>-1.4253</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0057</v>
+        <v>0.2174</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9311</v>
+        <v>-0.028</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>0.2453</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9179</v>
+        <v>-1.5569</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0566</v>
+        <v>0.1137</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1387</v>
+        <v>-1.6706</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>-2.7316</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8668</v>
+        <v>0.7085</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.378</v>
+        <v>0.176</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4888</v>
+        <v>0.5325</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3856</v>
+        <v>0.9317</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7997</v>
+        <v>1.2472</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1853</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="21">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5836</v>
+        <v>-0.711</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2589</v>
+        <v>-0.2636</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3247</v>
+        <v>-0.4474</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6211</v>
+        <v>-0.6227</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7784</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1893</v>
+        <v>-0.1939</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1893</v>
+        <v>-0.1939</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0375</v>
+        <v>-0.0882</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1071</v>
+        <v>-0.0185</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.846</v>
+        <v>-0.9548</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9394</v>
+        <v>-3.9929</v>
       </c>
       <c r="F22" t="n">
-        <v>3.0934</v>
+        <v>3.0381</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7123</v>
+        <v>-0.7272</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.512</v>
+        <v>-1.5271</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7997</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8575</v>
+        <v>-0.9031</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.6358</v>
+        <v>-1.6697</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7782</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1452</v>
+        <v>0.1759</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1238</v>
+        <v>0.1426</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2273</v>
+        <v>1.1382</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5474</v>
+        <v>0.5523</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.5859</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5294</v>
+        <v>-1.2858</v>
       </c>
       <c r="E23" t="n">
-        <v>2.8013</v>
+        <v>2.8755</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.3307</v>
+        <v>-4.1613</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1776</v>
+        <v>-0.1892</v>
       </c>
       <c r="H23" t="n">
         <v>0.9046999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0823</v>
+        <v>-1.0939</v>
       </c>
       <c r="J23" t="n">
-        <v>2.244</v>
+        <v>2.2023</v>
       </c>
       <c r="K23" t="n">
-        <v>2.0709</v>
+        <v>2.0544</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1731</v>
+        <v>0.1478</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4215</v>
+        <v>-2.3915</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1662</v>
+        <v>-1.1497</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2554</v>
+        <v>-1.2417</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3799</v>
+        <v>0.6271</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4615</v>
+        <v>0.5881</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.7782</v>
+        <v>-4.0996</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.354</v>
+        <v>-4.0234</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4242</v>
+        <v>-0.0762</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.8722</v>
+        <v>-3.8747</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1906</v>
+        <v>-1.181</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.6816</v>
+        <v>-2.6938</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.3801</v>
+        <v>-3.4029</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7171</v>
+        <v>-0.7207</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.663</v>
+        <v>-2.6822</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4921</v>
+        <v>-0.4719</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7848000000000001</v>
+        <v>-0.1173</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.747</v>
+        <v>-0.3929</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0378</v>
+        <v>0.2755</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0285</v>
+        <v>-1.018</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0285</v>
+        <v>-1.018</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.048</v>
+        <v>-6.6584</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.493499999999999</v>
+        <v>-9.43</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4455</v>
+        <v>2.7715</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.8631</v>
+        <v>-4.8679</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.1816</v>
+        <v>-2.1882</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.6815</v>
+        <v>-2.6797</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.107</v>
+        <v>-5.1452</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.9345</v>
+        <v>-2.9625</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.1725</v>
+        <v>-2.1827</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2439</v>
+        <v>0.2773</v>
       </c>
       <c r="N25" t="n">
-        <v>0.7529</v>
+        <v>0.7743</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.3265</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1693</v>
+        <v>-0.0492</v>
       </c>
       <c r="U25" t="n">
-        <v>0.094</v>
+        <v>0.3757</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.0381</v>
+        <v>-7.6561</v>
       </c>
       <c r="E26" t="n">
-        <v>-14.1149</v>
+        <v>-14.4428</v>
       </c>
       <c r="F26" t="n">
-        <v>4.0768</v>
+        <v>6.786600000000002</v>
       </c>
       <c r="G26" t="n">
-        <v>-7.2496</v>
+        <v>-7.2371</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7068999999999996</v>
+        <v>0.7174000000000005</v>
       </c>
       <c r="I26" t="n">
-        <v>-7.9566</v>
+        <v>-7.954499999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.7837</v>
+        <v>-2.033499999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>2.455400000000001</v>
+        <v>2.305700000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>-4.238999999999999</v>
+        <v>-4.3393</v>
       </c>
       <c r="M26" t="n">
-        <v>-5.4661</v>
+        <v>-5.2036</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.7485</v>
+        <v>-1.5883</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.7175</v>
+        <v>-3.6152</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.402600000000001</v>
+        <v>-3.414499999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-19.2808</v>
+        <v>-19.3487</v>
       </c>
       <c r="R26" t="n">
-        <v>15.8782</v>
+        <v>15.9342</v>
       </c>
       <c r="S26" t="n">
-        <v>1.482</v>
+        <v>3.855799999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1361999999999998</v>
+        <v>0.1583999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>1.3457</v>
+        <v>3.6972</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.8677999999999995</v>
+        <v>-0.8602000000000003</v>
       </c>
       <c r="W26" t="n">
-        <v>6.8132</v>
+        <v>6.7809</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.681</v>
+        <v>-7.641100000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104655_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104655_W22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.2361</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.018</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104655_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-7.641100000000001</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
